--- a/策划/数值文档/card_cs-pack.xlsx
+++ b/策划/数值文档/card_cs-pack.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>id</t>
   </si>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>card_spear-goblins</t>
+  </si>
+  <si>
+    <t>chr_goblin_archer_out</t>
   </si>
   <si>
     <t>giant</t>
@@ -962,7 +965,7 @@
         <v>44</v>
       </c>
       <c r="J8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K8" t="s">
         <v>30</v>
@@ -973,13 +976,13 @@
         <v>26010005</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -994,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" t="s">
         <v>30</v>
@@ -1008,13 +1011,13 @@
         <v>26010007</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1029,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K10" t="s">
         <v>30</v>
@@ -1043,13 +1046,13 @@
         <v>26010010</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1064,10 +1067,10 @@
         <v>6</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K11" t="s">
         <v>30</v>
@@ -1078,13 +1081,13 @@
         <v>26010011</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1099,10 +1102,10 @@
         <v>3</v>
       </c>
       <c r="I12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K12" t="s">
         <v>30</v>
@@ -1113,13 +1116,13 @@
         <v>26010012</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1134,10 +1137,10 @@
         <v>2</v>
       </c>
       <c r="I13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K13" t="s">
         <v>30</v>
@@ -1148,13 +1151,13 @@
         <v>26010014</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1169,10 +1172,10 @@
         <v>2</v>
       </c>
       <c r="I14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K14" t="s">
         <v>30</v>
@@ -1183,13 +1186,13 @@
         <v>26010015</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1204,10 +1207,10 @@
         <v>2</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s">
         <v>30</v>
@@ -1218,13 +1221,13 @@
         <v>26010016</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1239,10 +1242,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s">
         <v>30</v>
@@ -1253,13 +1256,13 @@
         <v>26010017</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1274,10 +1277,10 @@
         <v>6</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K17" t="s">
         <v>30</v>
@@ -1288,13 +1291,13 @@
         <v>26010019</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1309,10 +1312,10 @@
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s">
         <v>30</v>
@@ -1323,13 +1326,13 @@
         <v>26010020</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1344,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K19" t="s">
         <v>30</v>
@@ -1358,13 +1361,13 @@
         <v>26010022</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1379,10 +1382,10 @@
         <v>5</v>
       </c>
       <c r="I20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K20" t="s">
         <v>30</v>
@@ -1393,13 +1396,13 @@
         <v>26010041</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -1414,10 +1417,10 @@
         <v>3</v>
       </c>
       <c r="I21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K21" t="s">
         <v>30</v>
@@ -1428,13 +1431,13 @@
         <v>26010051</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1449,10 +1452,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K22" t="s">
         <v>30</v>
@@ -1463,13 +1466,13 @@
         <v>26010052</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1484,10 +1487,10 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K23" t="s">
         <v>30</v>
@@ -1498,13 +1501,13 @@
         <v>26010058</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -1519,10 +1522,10 @@
         <v>5</v>
       </c>
       <c r="I24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K24" t="s">
         <v>30</v>
